--- a/request_forms/020_process_efficiency_collaboration_application_form--request_forms.xlsx
+++ b/request_forms/020_process_efficiency_collaboration_application_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>process_efficiency_collaboration_application_form_1</t>
+          <t>process_efficiency_collaboration_form_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Process Improvement Idea</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Improvement Idea</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please describe your improvement idea</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,7 +547,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>process_efficiency_collaboration_application_form_2</t>
+          <t>process_efficiency_collaboration_form_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -551,10 +555,14 @@
           <t>Collaboration Method</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>How would you like to collaborate?</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,7 +574,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>process_efficiency_collaboration_application_form_3</t>
+          <t>process_efficiency_collaboration_form_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -574,10 +582,14 @@
           <t>Submission Date</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Select a date for your submission</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,7 +601,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>process_efficiency_collaboration_application_form_4</t>
+          <t>process_efficiency_collaboration_form_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -597,10 +609,14 @@
           <t>Submission Time</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select a time for your submission</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,7 +628,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>process_efficiency_collaboration_application_form_5</t>
+          <t>process_efficiency_collaboration_form_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -620,10 +636,14 @@
           <t>Contact Information</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter your contact email address</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,7 +655,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>process_efficiency_collaboration_application_form_6</t>
+          <t>process_efficiency_collaboration_form_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -643,7 +663,11 @@
           <t>Phone Number</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter your phone number</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -658,7 +682,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>process_efficiency_collaboration_application_form_7</t>
+          <t>process_efficiency_collaboration_form_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -666,7 +690,11 @@
           <t>Additional Comments</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please provide any additional comments</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,7 +709,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>process_efficiency_collaboration_application_form_8</t>
+          <t>process_efficiency_collaboration_form_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -689,10 +717,14 @@
           <t>Submission Status</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select the status of your submission</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +736,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>process_efficiency_collaboration_application_form_9</t>
+          <t>process_efficiency_collaboration_form_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Submission Date</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Process Efficiency Collaboration Form 9</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select a date for your submission</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +763,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>process_efficiency_collaboration_application_form_10</t>
+          <t>process_efficiency_collaboration_form_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Submission Time</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Process Efficiency Collaboration Form 10</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Select a time for your submission</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +790,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>process_efficiency_collaboration_application_form_11</t>
+          <t>process_efficiency_collaboration_form_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Contact Information</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Process Efficiency Collaboration Form 11</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Enter your contact information</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,16 +817,182 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>process_efficiency_collaboration_application_form_12</t>
+          <t>process_efficiency_collaboration_form_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phone Number</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Process Efficiency Collaboration Form 12</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Enter your phone number</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>process_efficiency_collaboration_form_13</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Submission Reason</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please describe the reason for your submission</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>process_efficiency_collaboration_form_14</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Submission Location</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please select the location of your submission</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>process_efficiency_collaboration_form_15</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Submission Type</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please select the type of your submission</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>process_efficiency_collaboration_form_16</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Submission Frequency</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please select the frequency of your submission</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>process_efficiency_collaboration_form_17</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Submission Time Frame</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please select the time frame of your submission</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>process_efficiency_collaboration_form_18</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Submission Deadline</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Please select the submission deadline</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -799,12 +1009,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,58 +1037,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>process_efficiency_collaboration_application_form_2_choices</t>
+          <t>process_efficiency_collaboration_form_2_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>collaboration</t>
+          <t>option_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Option A</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>process_efficiency_collaboration_application_form_2_choices</t>
+          <t>process_efficiency_collaboration_form_2_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>inclusion</t>
+          <t>option_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Inclusion</t>
+          <t>Option B</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>process_efficiency_collaboration_application_form_2_choices</t>
+          <t>process_efficiency_collaboration_form_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>exclusion</t>
+          <t>option_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Exclusion</t>
+          <t>Option C</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>process_efficiency_collaboration_application_form_8_choices</t>
+          <t>process_efficiency_collaboration_form_8_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -895,7 +1105,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>process_efficiency_collaboration_application_form_8_choices</t>
+          <t>process_efficiency_collaboration_form_8_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -912,7 +1122,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>process_efficiency_collaboration_application_form_8_choices</t>
+          <t>process_efficiency_collaboration_form_8_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -923,6 +1133,142 @@
       <c r="C7" t="inlineStr">
         <is>
           <t>Cancelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>process_efficiency_collaboration_form_14_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>option_a</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>process_efficiency_collaboration_form_14_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>option_b</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>process_efficiency_collaboration_form_15_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>option_c</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>process_efficiency_collaboration_form_15_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>option_d</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>process_efficiency_collaboration_form_16_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>option_e</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Option E</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>process_efficiency_collaboration_form_16_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>option_f</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Option F</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>process_efficiency_collaboration_form_17_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>option_g</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Option G</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>process_efficiency_collaboration_form_17_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>option_h</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Option H</t>
         </is>
       </c>
     </row>
